--- a/Paper/_statistics/detector.xlsx
+++ b/Paper/_statistics/detector.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benel\Coding\Python\Paper\_statistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8C4C1A-2469-4BAB-A8AE-F7A753799C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E25A3EC-4746-4B57-BA25-42C20A33608F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48012" yWindow="1644" windowWidth="21600" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32760" yWindow="2025" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="table_3" sheetId="1" r:id="rId1"/>
     <sheet name="table_4" sheetId="2" r:id="rId2"/>
+    <sheet name="table_5" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="36">
   <si>
     <t>detector</t>
   </si>
@@ -127,6 +128,27 @@
   </si>
   <si>
     <t>never_recovered_before_next_crisis</t>
+  </si>
+  <si>
+    <t>cash</t>
+  </si>
+  <si>
+    <t>fallback</t>
+  </si>
+  <si>
+    <t>hrp</t>
+  </si>
+  <si>
+    <t>delta_ptt</t>
+  </si>
+  <si>
+    <t>delta_ttp</t>
+  </si>
+  <si>
+    <t>delta_full</t>
+  </si>
+  <si>
+    <t>regime</t>
   </si>
 </sst>
 </file>
@@ -170,9 +192,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -223,6 +244,10 @@
             <v>514</v>
           </cell>
         </row>
+        <row r="4">
+          <cell r="F4"/>
+          <cell r="H4"/>
+        </row>
         <row r="5">
           <cell r="F5">
             <v>16</v>
@@ -243,6 +268,7 @@
           <cell r="F7">
             <v>-34</v>
           </cell>
+          <cell r="H7"/>
         </row>
         <row r="8">
           <cell r="F8">
@@ -356,6 +382,14 @@
             <v>523</v>
           </cell>
         </row>
+        <row r="22">
+          <cell r="F22"/>
+          <cell r="H22"/>
+        </row>
+        <row r="23">
+          <cell r="F23"/>
+          <cell r="H23"/>
+        </row>
         <row r="24">
           <cell r="F24">
             <v>-442</v>
@@ -368,6 +402,7 @@
           <cell r="F25">
             <v>-114</v>
           </cell>
+          <cell r="H25"/>
         </row>
         <row r="26">
           <cell r="F26">
@@ -489,6 +524,10 @@
             <v>-57</v>
           </cell>
         </row>
+        <row r="41">
+          <cell r="F41"/>
+          <cell r="H41"/>
+        </row>
         <row r="42">
           <cell r="F42">
             <v>-442</v>
@@ -501,6 +540,7 @@
           <cell r="F43">
             <v>-94</v>
           </cell>
+          <cell r="H43"/>
         </row>
         <row r="44">
           <cell r="F44">
@@ -518,6 +558,14 @@
             <v>-43</v>
           </cell>
         </row>
+        <row r="46">
+          <cell r="F46"/>
+          <cell r="H46"/>
+        </row>
+        <row r="47">
+          <cell r="F47"/>
+          <cell r="H47"/>
+        </row>
         <row r="48">
           <cell r="F48">
             <v>63</v>
@@ -550,6 +598,14 @@
             <v>145</v>
           </cell>
         </row>
+        <row r="52">
+          <cell r="F52"/>
+          <cell r="H52"/>
+        </row>
+        <row r="53">
+          <cell r="F53"/>
+          <cell r="H53"/>
+        </row>
         <row r="54">
           <cell r="F54">
             <v>-63</v>
@@ -582,6 +638,14 @@
             <v>963</v>
           </cell>
         </row>
+        <row r="58">
+          <cell r="F58"/>
+          <cell r="H58"/>
+        </row>
+        <row r="59">
+          <cell r="F59"/>
+          <cell r="H59"/>
+        </row>
         <row r="60">
           <cell r="F60">
             <v>-251</v>
@@ -594,6 +658,11 @@
           <cell r="F61">
             <v>-30</v>
           </cell>
+          <cell r="H61"/>
+        </row>
+        <row r="62">
+          <cell r="F62"/>
+          <cell r="H62"/>
         </row>
         <row r="63">
           <cell r="F63">
@@ -603,10 +672,23 @@
             <v>-43</v>
           </cell>
         </row>
+        <row r="64">
+          <cell r="F64"/>
+          <cell r="H64"/>
+        </row>
+        <row r="65">
+          <cell r="F65"/>
+          <cell r="H65"/>
+        </row>
+        <row r="66">
+          <cell r="F66"/>
+          <cell r="H66"/>
+        </row>
         <row r="67">
           <cell r="F67">
             <v>-30</v>
           </cell>
+          <cell r="H67"/>
         </row>
         <row r="68">
           <cell r="F68">
@@ -624,6 +706,14 @@
             <v>209</v>
           </cell>
         </row>
+        <row r="70">
+          <cell r="F70"/>
+          <cell r="H70"/>
+        </row>
+        <row r="71">
+          <cell r="F71"/>
+          <cell r="H71"/>
+        </row>
         <row r="72">
           <cell r="F72">
             <v>1</v>
@@ -636,6 +726,7 @@
           <cell r="F73">
             <v>-30</v>
           </cell>
+          <cell r="H73"/>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
@@ -960,22 +1051,22 @@
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>0.48720000000000002</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>343</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>10</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>0.67449999999999999</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2">
         <v>0.25729999999999997</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2">
         <v>1.38</v>
       </c>
       <c r="I2">
@@ -992,22 +1083,22 @@
       <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
         <v>0.2324</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>156</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>0.57440000000000002</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3">
         <v>0.45929999999999999</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3">
         <v>2.46</v>
       </c>
       <c r="I3">
@@ -1024,22 +1115,22 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>0.4108</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>26</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>110</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>0.75090000000000001</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4">
         <v>0.3397</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4">
         <v>1.82</v>
       </c>
       <c r="I4">
@@ -1056,22 +1147,22 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>0.48730000000000001</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>381</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>9</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>0.68140000000000001</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5">
         <v>0.25990000000000002</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>1.39</v>
       </c>
       <c r="I5">
@@ -1088,22 +1179,22 @@
       <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6">
         <v>0.22259999999999999</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>49</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>32</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>0.47970000000000002</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6">
         <v>0.40050000000000002</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>2.15</v>
       </c>
       <c r="I6">
@@ -1120,22 +1211,22 @@
       <c r="B7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7">
         <v>0.39710000000000001</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>68</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>41</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>0.7288</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7">
         <v>0.34100000000000003</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>1.83</v>
       </c>
       <c r="I7">
@@ -1152,22 +1243,22 @@
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8">
         <v>0.4909</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>384</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>9</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>0.68669999999999998</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8">
         <v>0.26</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>1.39</v>
       </c>
       <c r="I8">
@@ -1184,22 +1275,22 @@
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9">
         <v>0.2147</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>101</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>15</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>0.4224</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9">
         <v>0.36570000000000003</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>1.96</v>
       </c>
       <c r="I9">
@@ -1216,22 +1307,22 @@
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10">
         <v>0.4289</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>144</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>21</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>0.64780000000000004</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10">
         <v>0.28070000000000001</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>1.5</v>
       </c>
       <c r="I10">
@@ -1248,22 +1339,22 @@
       <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11">
         <v>0.53500000000000003</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>628</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>0.73939999999999995</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11">
         <v>0.25690000000000002</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>1.38</v>
       </c>
       <c r="I11">
@@ -1280,22 +1371,22 @@
       <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12">
         <v>0.1779</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>251</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>5</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>0.21920000000000001</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12">
         <v>0.22900000000000001</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>1.23</v>
       </c>
       <c r="I12">
@@ -1312,22 +1403,22 @@
       <c r="B13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13">
         <v>0.39219999999999999</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>345</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>8</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>0.59119999999999995</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13">
         <v>0.2802</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>1.5</v>
       </c>
       <c r="I13">
@@ -1633,4 +1724,78 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B8359C0-4A02-425C-970B-AE098ACD6005}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>